--- a/public/templates/forms/A-005-RACIMatrixforCybersecurity-FORM.xlsx
+++ b/public/templates/forms/A-005-RACIMatrixforCybersecurity-FORM.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="12">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
@@ -426,12 +426,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
